--- a/docs/04_3日間チャレンジ_コンセプト・設計.xlsx
+++ b/docs/04_3日間チャレンジ_コンセプト・設計.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3日間設計" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進行表60分" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特典設計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day1_自己紹介主軸案" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,6 +108,20 @@
       <color rgb="00555555"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -151,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -173,11 +188,102 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -254,6 +360,39 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -633,6 +772,8 @@
           <t>3日間チャレンジ｜コンセプト設計（確定版 v2）</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="27" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -640,6 +781,8 @@
           <t>セミナー名（確定）：保険営業から、社長の"相談役"へ ― 会計を武器に法人を開く3日間チャレンジ</t>
         </is>
       </c>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="27" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -647,6 +790,8 @@
           <t>■ 1枚定義（このセミナーは何か）</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -659,6 +804,7 @@
           <t>個人保険で頭打ちの保険営業（本命＝A型「頭打ち中堅」35〜50代・年収500〜650万）</t>
         </is>
       </c>
+      <c r="C4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -671,6 +817,7 @@
           <t>3日間で「決算書から社長の悩みを当て、効く保険まで見える」体験 →「保険屋」から相談役へ</t>
         </is>
       </c>
+      <c r="C5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -683,6 +830,7 @@
           <t>会計を武器に「利益は出ているのに残らない＝お金の残し方/守り方」を解き、決算書から保険ニーズへ翻訳できる（当事者性＋実例＝競合の白地）</t>
         </is>
       </c>
+      <c r="C6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -695,6 +843,7 @@
           <t>個別相談 → A30万（自走）/B300万（伴走）。育ったFPが経営者を連れてくる循環の起点</t>
         </is>
       </c>
+      <c r="C7" s="27" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -702,6 +851,8 @@
           <t>背骨：会計で入口を作り、保険で締める。入口（決算書・お金の残し方）は相談役の信頼を取る手段、本丸は“避けられない大きな支出”を保険で備えること。</t>
         </is>
       </c>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="27" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -709,6 +860,8 @@
           <t>■ コンセプト（一言で）</t>
         </is>
       </c>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="27" t="n"/>
     </row>
     <row r="10" ht="84" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -716,6 +869,8 @@
           <t>保険を"売りに行く"のをやめる。決算書を片手に『利益は出ているのに、なぜか手元にお金が残らない』を社長と一緒に解く"相談役"になる。すると、現金の薄いその会社が“社長の万一・退職・相続・事業承継”という避けられない大きな支出に無防備だと見えてくる——そこは資金繰りでは用意できない、保険でしか備えられない。だから保険は、相談役になった結果、後からついてくる。</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -728,6 +883,7 @@
           <t>"保険屋"から、社長の相談役へ。― 決算書で「利益は出ているのに残らないお金」を解く3日間。</t>
         </is>
       </c>
+      <c r="C11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -740,6 +896,7 @@
           <t>決算書が読めれば、保険は"売り込まなくても"ついてくる。</t>
         </is>
       </c>
+      <c r="C12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -752,6 +909,7 @@
           <t>社長は"保険屋"には会わない。でも"数字がわかる人"には会う。</t>
         </is>
       </c>
+      <c r="C13" s="27" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -759,6 +917,8 @@
           <t>■ 差別化の3点（“ありきたり”を避ける生命線）</t>
         </is>
       </c>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -771,6 +931,7 @@
           <t>中身</t>
         </is>
       </c>
+      <c r="C15" s="27" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -783,6 +944,7 @@
           <t>「利益は出ているのに残らない＝お金の残し方／守り方」を語り、決算書から保険ニーズへ翻訳できる（競合の白地）</t>
         </is>
       </c>
+      <c r="C16" s="27" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -795,6 +957,7 @@
           <t>藤山＝“数字が読めず苦しんだ当事者”からの転換（実績自慢でなく痛みへの共感／自虐でなく前向き）</t>
         </is>
       </c>
+      <c r="C17" s="27" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -807,6 +970,7 @@
           <t>知識講義でなく、その場で決算書から社長を“当てる”小さな成功（変化量＞情報量）</t>
         </is>
       </c>
+      <c r="C18" s="27" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -814,6 +978,8 @@
           <t>■ これは“何でないか”（輪郭）</t>
         </is>
       </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="27" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -821,6 +987,8 @@
           <t>× 保険の売り方講座でない（保険は後からついてくる）</t>
         </is>
       </c>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="27" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -828,6 +996,8 @@
           <t>× 会計コンサル／財務改善コンサルでない（資金繰り改善は“入口”。本丸は決算書から見える“備えるべきお金”を保険で用意すること）</t>
         </is>
       </c>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="27" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -835,6 +1005,8 @@
           <t>× 決算書知識の詰め込み講義でない（変化量＞情報量・1日1ゴール）</t>
         </is>
       </c>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="27" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -842,6 +1014,8 @@
           <t>× 節税スキームの伝授でない（2019年改正で“節税で売る時代”は終了）</t>
         </is>
       </c>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="27" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -849,6 +1023,8 @@
           <t>× ありきたりの“相談役”ポジショントークでない（取り方＋当事者性で差別化）</t>
         </is>
       </c>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -856,6 +1032,8 @@
           <t>× 「管理会計」を看板にしない（会計は手法であって目的でない・語は伏せ、たとえ→用語）</t>
         </is>
       </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="27" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -863,6 +1041,8 @@
           <t>■ ★保険への接続線（なぜ相談役→保険になるのか）</t>
         </is>
       </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="27" t="n"/>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -870,6 +1050,8 @@
           <t>日々の“資金繰り改善”は入口（相談役の信頼を取る手段）。本丸は、決算書から見える“避けられない大きな支出”を保険で備えること。資金繰り改善は会計コンサルでもできるが、“将来の大きな支出を現金で備える”はFP（保険）の独壇場。会計で入口を作り、保険で締める。</t>
         </is>
       </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="27" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -962,6 +1144,8 @@
           <t>■ WHY NOW（なぜ今か＝学ぶ理由）</t>
         </is>
       </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -969,6 +1153,8 @@
           <t>・ 個人は飽和（世帯加入率89.2%・死亡保障額は2009年以降一貫減）＝新規は奪い合い</t>
         </is>
       </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="27" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -976,6 +1162,8 @@
           <t>・ 節税で売る時代は2019年に終了（通達4区分）＝商品売りモデルの寿命</t>
         </is>
       </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="27" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -983,6 +1171,8 @@
           <t>・ AI・比較サイトで“説明係”は中抜き＝代替されない相談役だけが残る</t>
         </is>
       </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="27" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -990,6 +1180,8 @@
           <t>・ 事業承継は時限（特例の適用2027/12/31・自社株評価見直し早ければ2028/1）＝今がピーク帯</t>
         </is>
       </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="27" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -997,6 +1189,8 @@
           <t>※営業マン個人では変えられない構造変化＝だから今学んで立ち位置を変える。煽らず「平時でも構造的に残りにくい」恒常論で。「倒産の半数が黒字」は不使用。</t>
         </is>
       </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="27" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -1004,6 +1198,8 @@
           <t>■ 参加者の最終ゴール（Before → After）</t>
         </is>
       </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="27" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -1096,6 +1292,8 @@
           <t>一文で：保険屋として消耗していた人が、“決算書で社長の悩みを当て、そこに保険が効くと分かった自分”を体験し、相談役になる道（個別相談）を選んで帰る。</t>
         </is>
       </c>
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="27" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -1103,6 +1301,8 @@
           <t>■ 事業ゴール（KPI）</t>
         </is>
       </c>
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="27" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1115,6 +1315,7 @@
           <t>個別相談 予約率（Day3参加者比）＝無料3日間の“成功”はここ</t>
         </is>
       </c>
+      <c r="C47" s="27" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1127,6 +1328,7 @@
           <t>個別相談 → プランA(30万)／プランB(300万) 成約</t>
         </is>
       </c>
+      <c r="C48" s="27" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -1139,6 +1341,7 @@
           <t>登録率・Day1参加率・Day3残存率・ワーク提出率（関与）</t>
         </is>
       </c>
+      <c r="C49" s="27" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1151,6 +1354,7 @@
           <t>Day3まで出さない／割引なし（動機づけは期限付き特典）／数値目標は初回で基準づくり〔仮〕</t>
         </is>
       </c>
+      <c r="C50" s="27" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -1158,6 +1362,8 @@
           <t>■ チャレンジ“成功”の定義（買う/買わないに関わらず）</t>
         </is>
       </c>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="27" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -1165,6 +1371,8 @@
           <t>・ 参加者が自分の悩み（保険屋としての消耗）を自分の言葉で言える</t>
         </is>
       </c>
+      <c r="B52" s="26" t="n"/>
+      <c r="C52" s="27" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -1172,6 +1380,8 @@
           <t>・ 決算書から社長の悩みを1つ当てられた＝「自分にもできそう」</t>
         </is>
       </c>
+      <c r="B53" s="26" t="n"/>
+      <c r="C53" s="27" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -1179,6 +1389,8 @@
           <t>・ 講師・運営・仲間に信頼を持っている／「参加してよかった」</t>
         </is>
       </c>
+      <c r="B54" s="26" t="n"/>
+      <c r="C54" s="27" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -1186,6 +1398,8 @@
           <t>・ 購入者は次の行動が明確、未購入者にも“相談役”という考え方が残る</t>
         </is>
       </c>
+      <c r="B55" s="26" t="n"/>
+      <c r="C55" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -1590,6 +1804,9 @@
           <t>※各60分（20:00–21:00）。Day3は60分制約のため、B(300万)と詳細Q&amp;Aは個別相談に寄せる。録画＝期限付きアーカイブ／公式LINE登録者限定。税務数値は知識ドメイン_リサーチと一致＋コンプラ注意書き（情報提供にとどめる）。</t>
         </is>
       </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1981,6 +2198,11 @@
           <t>特典（プレゼント）設計 ― 補助輪＝“理想未来に近づく”／delivery主体ゆえ“読めば再現できる”完成度が生命線／割引なし＝期限付き特典／負の感情NG・ポジティブ＆実務直結</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -2308,6 +2530,11 @@
           <t>※「数で魅せる」（点数を多く見せる）が、各々が“補助輪”。割引はしない＝期限付き特典で動機づけ。税務に触れる特典は税理士法・保険業法＝情報提供にとどめる＋知識ドメインと数値一致。公式LINE登録特典(S)は7/1までに確定。</t>
         </is>
       </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2316,4 +2543,934 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Day1 設計改訂案（藤山ストーリー主軸）｜2026-07-03 議論まとめ（同日追記：自分事化ブロック）｜状態：検討中（04・06未反映／スライド未作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>方針：Day1＝藤山の自己紹介（どんな人間か→過去の失敗→今→なぜこのセミナーか）を主軸に、業界の現在進行形の危機（市場・FP過剰・プルデンシャル事件）で自分事化し、参加FPの士気を高める日にする。★2026-07-04更新：構成は「威厳→失敗（心理の物語）→防具・相談役→使命→なぜあなたに→業界と機会→一緒に」へ改訂／「売り込みません」宣言は廃止／損失額＝トータル約10億円で確定（旧・約4億円規模は使用しない）／案件名・内訳・返済/清算には触れない／FBグループ表記は一般名のまま。最新の正＝docs/04_台本_Day1.md（v3）。本シートの進行表・文言案はv3原稿FIX後に更新する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>■ ワンメッセージ（Day1全体で証明する一文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>「会計から逃げて大失敗した藤山が、会計を武器に再起した。―― 保険営業のあなたも、決算書を武器に社長の"相談役"に変われる」</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>フック候補</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>①「過去72ヶ月、一度もマイナスの月がない」（冒頭のつかみ）　②「数字は見ていた。でも、読めていなかった」　③「理解できないものを二つ持つと、リスクは半分ではなく二倍になる」　④「会計は、武器である前に防具」　⑤「『取り戻しましょう』ではなく『まず傷口を広げないようにしましょう』と言える存在＝相談役」</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>■ 全日共通セットアップ（表紙直後に固定・★新設 2026-07-03指示）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>お約束（3つ）</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>1. 顔出しでご参加ください（カメラON）
+2. コメントで積極的に参加してください
+3. セミナー終了後、Facebookグループに感想を必ず投稿してください</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>理由（前段に置く）</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>この3日間は「視聴」ではなく「参加」で成果が決まります。コメントした人・ワークを出した人から変わっていきます。</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>退出ルール</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>※お約束いただけない場合は、途中でも強制退出となります。→ 強さは残す（本気のフィルター）。前段の「なぜルールがあるか」とセットで、丁寧語トーンは維持（voice-guide準拠）。</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>運用メモ</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>ワーク提出＝Facebookグループへのコメント投稿に一本化（KPI「ワーク提出率」の計測点もFBコメント数）。Day1〜3すべての資料の冒頭に同一スライドを置く。</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>■ 「なぜ無料か」ブロック（冒頭で宣言 → ストーリーで回収・★新設 2026-07-03指示）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>解決する困りごと</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>・個人保険で頭打ち。紹介も枯れてきた
+・法人に行きたいが、決算書を前にすると固まってしまう
+・社長に会っても「保険屋さん」で終わり、話を聞いてもらえない</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>3日後のあなた</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>・決算書から社長の悩みを"当てられる"ようになる
+・「売りに行く人」から、社長に相談される側へ</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>無料の理由（使命）</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>私は、会計を知らないまま数字を信じて、約4億円規模の失敗をしました。お客様のお金に関わる人に、同じ失敗を絶対にしてほしくない。お客様と自分を守る「防具としての会計」を、一人でも多くのFPに届けたい。だからこの3日間は、無料ですべてお渡しします。</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>正直な予告</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>（最終日に、さらに深く学びたい方への案内だけ少しさせてください。それまでの売り込みは一切しません）→ Day3案内を先に開示して無料への警戒を外す＋「売り込みません」宣言と接続。冒頭の「4億円」の一言がストーリーパートへの引きになる。</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>■ Day1 進行 60分（改訂v2・業界ブロック追加）― 現行「進行表60分」シートの Day1 を置き換える案</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>変更点／ねらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>0–4</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>セットアップ（お約束3つ＋強制退出）</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>★新設・全日共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>4–9</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>なぜ無料か（困りごと→3日後の姿→理由）＋今日のゴール＋「今日は売り込みません」宣言</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>★新設。「4億円」で引きを作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>9–13</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>どんな人間か：三井住友海上→独立、4カ国8業種</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>挑戦者としての好感</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>13–24</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>FX編:72ヶ月連続プラス→確信→合同会社→ポンドショック・ウクライナ侵攻→取り戻し心理→月30%話→約4億円規模</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>山場①「数字を見る≠読む」</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>24–28</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>医療事業編（圧縮3〜4分）：分散のつもりが同じ失敗</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>教訓の再現性（一度の不運にしない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>28–34</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>気づき：会計は武器である前に防具／「傷口を広げない」と言える存在＝相談役</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>山場②WHYの核心</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>34–39</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>今：再起の証明（実績5カテゴリ）＋ミッション＝冒頭「なぜ無料か」の回収</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>希望と信頼性</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>39–47</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>★あなたの業界の数字を読む（自分事化）：市場の数字→プレイヤーの数字→信頼の数字（プルデンシャル）→機会の予告</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>★新設 2026-07-03指示。藤山の危機→あなたの業界の危機へブリッジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>47–54</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>だからFPこそ会計を → ワーク（その場で書き始め→完成版はFBコメントで提出）</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>士気→自分ごと化。ワーク提出をルール③と一体化し時間を捻出</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>54–60</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>シェア・承認・Day2予告（「社長の困りごとを数字で当てる」＋承継市場の空白）・特典案内・FB投稿の再喚起</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>ルール③をクロージングで再度押す</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>※現行Day1の「会社の数字の全体像（持ち物・稼ぎ・財布のたとえ＋決算書1枚デモ）」は Day2冒頭へ移動が必要（04改訂事項）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>■ 自分事化ブロック「あなたの業界の数字を読む」詳細（39–47・★新設 2026-07-03指示）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>位置づけ・枠組み</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>藤山ストーリーの直後に置くブリッジ。「私は自分の事業の数字を読めずに4億円を失いました。では、あなたは"自分の事業"＝保険営業という仕事の数字を読んだことがありますか？」→ 業界データを「他人の決算書を読む前に、まず自分の業界の数字を読む」練習として提示（セミナーのスキルの初体験を兼ねる）。危機で終わらせず「あなたはどちら側に立つか」で士気に変換。</t>
+        </is>
+      </c>
+      <c r="C35" s="38" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>数字（すべてresearch一次確認済み）</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>言いたいこと</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>出典・確度</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>【市場】世帯加入率89.2%（ピーク95%・1994）／世帯死亡保障額1,936万円・2009年以降一貫減</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>未加入世帯はほぼ残っていない＝新規は奪い合い。頭数も単価も縮む</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>生命保険文化センター・生命保険協会／高</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>【プレイヤー】生保営業職員24.2万人＋募集人91.4万人（7年連続減）／AFP15.2万・CFP2.8万・FP技能士延べ173万人／MDRTは約2%／5年目在籍率25%</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>「FPが多い」＝同じ武器（商品知識・個人保険）で戦う人が飽和。5年で4人に3人が消える構造</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>生命保険協会・日本FP協会・きんざい・日経／高</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>【信頼】プルデンシャル生命事件：30年以上・社員/元社員100人超・顧客約500人・計約31億円詐取（2026/1公表）→金融庁立入検査（2026/4報道）・業務停止も視野と報道</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>業界全体への信頼が毀損。監督・募集人管理は強化の方向＝「保険屋」への視線は一段と厳しくなる。誠実な人ほど逆風→だからこそ「顧客のお金を守る側」の価値が上がる</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>会社公表・時事・財界オンライン／高（公表・報道）。処分は検査中＝断定しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>【機会・予告のみ】後継者未定127万社・黒字廃業51.5%（1枚チラ見せ）</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>同じ数字が「空白」も示す＝相談役の不在。「明日、この空白をどう突くかを数字でやります」→Day2への引き</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>中小企業庁・東京商工リサーチ／高。詳細はDay2（棲み分け）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>プルデンシャル取扱注意（コンプラ）</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>①公表事実・大手報道のみ、数字は「約」を付け出典を口頭明示　②個社批判・嘲笑にしない＝「業界の信頼の問題」として扱う（受講者に同社・大手生保の関係者がいる前提で敬意）　③行政処分は「業務停止も視野と報道されている」まで＝断定しない　④保険業法の今後も「監督・募集人管理が強まる方向」と方向性のみ　⑤登壇直前（7/14前）に最新状況を再確認し、処分発表があれば文言差し替え</t>
+        </is>
+      </c>
+      <c r="C41" s="38" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>Day2との棲み分け</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Day1＝業界側の数字（市場飽和・FP過剰・信頼）で危機の自分事化／Day2＝経営者側の数字（承継・黒字廃業・245万人）で機会の提示。重複させない（research §5 のDay別マッピング準拠）</t>
+        </is>
+      </c>
+      <c r="C42" s="38" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>■ ワーク（ストーリー接続型・差し替え案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>自分が「72ヶ月連続プラス」を信じかけた（見た目の数字で判断した）経験を一つ書く</t>
+        </is>
+      </c>
+      <c r="C45" s="38" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>自分のお客様で「守れていないかもしれない」と顔が浮かぶ人を一人思い浮かべる</t>
+        </is>
+      </c>
+      <c r="C46" s="38" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>その人を守るために、明日のDay2で何を持ち帰りたいか一文 → ②③がそのままDay2への引きになる</t>
+        </is>
+      </c>
+      <c r="C47" s="38" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>その場で書き始め（5分）→ 完成版はセミナー後にFacebookグループへコメント投稿＝提出（ルール③と一体化）</t>
+        </is>
+      </c>
+      <c r="C48" s="38" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>■ 論点と推奨（2026-07-03 議論）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>論点</t>
+        </is>
+      </c>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>理由・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>① 4億円・預かり金・連帯保証をどこまで出すか</t>
+        </is>
+      </c>
+      <c r="B52" s="35" t="inlineStr">
+        <is>
+          <t>全部出す</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>同業の聴衆には隠すより開く方が信頼。ぼかすと逆に疑われる。ただし「迷惑をかけた方へのその後（返済・清算）」の一行が必須 → 藤山さん確認待ち（唯一の穴）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="inlineStr">
+        <is>
+          <t>② 医療事業編（後半）を入れるか</t>
+        </is>
+      </c>
+      <c r="B53" s="35" t="inlineStr">
+        <is>
+          <t>入れる（3〜4分に圧縮）</t>
+        </is>
+      </c>
+      <c r="C53" s="35" t="inlineStr">
+        <is>
+          <t>FX編だけだと「一度の不運」。医療編で「構造を読まないと同じ失敗を形を変えて繰り返す」という再現性のある教訓になる。「分散の誤解」はFPの実務にも直結</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>③ 現在の実績13件の見せ方</t>
+        </is>
+      </c>
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>全部並べず5カテゴリに集約</t>
+        </is>
+      </c>
+      <c r="C54" s="35" t="inlineStr">
+        <is>
+          <t>1)上場企業（年商530〜4400億）への幹部研修 2)地方銀行2行 3)年商数百億企業の資金調達・M&amp;A・承継 4)元東証・元アクセンチュアとの共同展開 5)平均AC2.5億円・TOT連続達成LPと共同経営（聴衆に一番効く）。役割は自慢でなく未来提示＝士気</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="inlineStr">
+        <is>
+          <t>④ ストーリー主軸だとマイクロリザルトが消える</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>ワークをストーリー接続型に差し替え</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="inlineStr">
+        <is>
+          <t>「感動したが何もできていない」日を防ぐ。書けた・気づけた＝小さな成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="inlineStr">
+        <is>
+          <t>⑤ 「武器」（現行コンセプト）と「防具」（新素材）の整合</t>
+        </is>
+      </c>
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>アークとして接続</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="inlineStr">
+        <is>
+          <t>Day1＝防具（守る・使命・WHY）→ Day2＝武器（当てる・スキル・HOW）→ Day3＝装備の揃え方（GAP→講座）。本人テキスト「法人開拓の武器である前に、防具です」が順序を定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="inlineStr">
+        <is>
+          <t>⑥ 業界動向をどこに置くか</t>
+        </is>
+      </c>
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>ストーリー直後（39–47）に「業界の数字を読む」として</t>
+        </is>
+      </c>
+      <c r="C57" s="35" t="inlineStr">
+        <is>
+          <t>単独の市況解説にせず、藤山の危機→あなたの業界の危機のブリッジ＋「数字を読む」初体験を兼ねる。60分の飽和はワーク提出のFB一体化で吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>■ Day1タイトル案〔仮〕（自己紹介主軸への変更に伴う再検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>現行〔仮〕</t>
+        </is>
+      </c>
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t>なぜ"数字がわかる保険屋"だけが、社長の隣に座れるのか</t>
+        </is>
+      </c>
+      <c r="C60" s="38" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>案A</t>
+        </is>
+      </c>
+      <c r="B61" s="33" t="inlineStr">
+        <is>
+          <t>数字は見ていた。でも、読めていなかった ― 4億円の失敗が教えてくれた、会計の本当の意味</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>案B</t>
+        </is>
+      </c>
+      <c r="B62" s="33" t="inlineStr">
+        <is>
+          <t>会計は、武器である前に防具 ― お客様を守れる保険営業になる3日間の初日</t>
+        </is>
+      </c>
+      <c r="C62" s="38" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>■ 事実関係アップデート（既存ドキュメントとの差分・要反映）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B65" s="34" t="inlineStr">
+        <is>
+          <t>既存の記載</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>今回の本人テキスト／新情報（2026-07-03）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t>損失規模</t>
+        </is>
+      </c>
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>「2桁億単位（仮・字幕誤変換の可能性）」（藤山ストーリー動画メモ）</t>
+        </is>
+      </c>
+      <c r="C66" s="35" t="inlineStr">
+        <is>
+          <t>「自己資金・預かり金・連帯保証を含め、およそ4億円規模」→ 本人記述を正とし「要裏取り」解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="35" t="inlineStr">
+        <is>
+          <t>失敗の中身</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="inlineStr">
+        <is>
+          <t>「8事業で大失敗」と抽象的</t>
+        </is>
+      </c>
+      <c r="C67" s="35" t="inlineStr">
+        <is>
+          <t>FX自動売買（72ヶ月連続プラス→ポンドショック・ウクライナ侵攻で崩壊）→月30%話→訪問診療事業（分散の誤解・連帯保証・知人巻き込み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="35" t="inlineStr">
+        <is>
+          <t>現在の実績</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="inlineStr">
+        <is>
+          <t>プライム上場・りそな総研・地銀の会計研修</t>
+        </is>
+      </c>
+      <c r="C68" s="35" t="inlineStr">
+        <is>
+          <t>＋年商280億〜4400億の企業群との取引、TOT連続達成LPと共同経営、元東証・元アクセンチュアとの連携 等13件</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="35" t="inlineStr">
+        <is>
+          <t>業界の信頼ショック</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="inlineStr">
+        <is>
+          <t>（未収録だった）</t>
+        </is>
+      </c>
+      <c r="C69" s="35" t="inlineStr">
+        <is>
+          <t>プルデンシャル事件 → research「法人保険営業の外部環境・リスク要因」§2へ収録済み（2026-07-03・出典付き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="36" t="inlineStr">
+        <is>
+          <t>→ 反映先（未実施）：docs/research/藤山ストーリー・経営者実態_動画メモ.md／docs/style/藤山泰成_プロフィール.md／04設計・進行表／06意思決定ログ／台本Day1　※外部環境リサーチへのプルデンシャル収録は実施済み（2026-07-03）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>■ 残確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>1. 藤山さんへ</t>
+        </is>
+      </c>
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>迷惑をかけた方への「その後（返済・清算）」に一行触れられるか（例：「今も返し続けています」等、事実ベース）。これが無いと感動が不信で終わるリスク</t>
+        </is>
+      </c>
+      <c r="C73" s="38" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>2. 運営</t>
+        </is>
+      </c>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>Facebookグループの有無・名称。LINE→FB招待の導線が必要なら 03集客設計へ反映</t>
+        </is>
+      </c>
+      <c r="C74" s="38" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>3. 登壇直前（7/14前）</t>
+        </is>
+      </c>
+      <c r="B75" s="33" t="inlineStr">
+        <is>
+          <t>プルデンシャル事件の最新状況を再確認（行政処分の発表があれば「業務停止も視野と報道」の文言を差し替え）</t>
+        </is>
+      </c>
+      <c r="C75" s="38" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B75:C75"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>